--- a/INTITUTO1/Client/wwwroot/CERTIFICADO.xlsx
+++ b/INTITUTO1/Client/wwwroot/CERTIFICADO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\source\repos\ITSC-Sistema-prueba2\INTITUTO1\Client\wwwroot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{550D70D7-CA3C-4B98-B5EE-7511E77DDA25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE494B9D-B98E-47A7-8D42-C591BC0483F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BD618E5C-7687-4DCA-9F98-F07F07A08645}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>C O N S T A N C I A  G E N E R A L</t>
   </si>
@@ -60,9 +60,6 @@
     <t xml:space="preserve">A pedido del interesado/a y al sólo efecto de ser presentada ante: </t>
   </si>
   <si>
-    <t xml:space="preserve">ANTE QUIEN CORRESPONDA </t>
-  </si>
-  <si>
     <t>se le extiende la presente constancia</t>
   </si>
   <si>
@@ -70,9 +67,6 @@
   </si>
   <si>
     <t xml:space="preserve"> días del mes de</t>
-  </si>
-  <si>
-    <t>OCTUBRE</t>
   </si>
   <si>
     <t xml:space="preserve"> del año</t>
@@ -1290,9 +1284,7 @@
       <c r="S20" s="16"/>
       <c r="T20" s="16"/>
       <c r="U20" s="16"/>
-      <c r="V20" s="23" t="s">
-        <v>11</v>
-      </c>
+      <c r="V20" s="23"/>
       <c r="W20" s="23"/>
       <c r="X20" s="23"/>
       <c r="Y20" s="23"/>
@@ -1338,7 +1330,7 @@
       <c r="V22" s="12"/>
       <c r="W22" s="12"/>
       <c r="X22" s="24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Y22" s="24"/>
       <c r="Z22" s="24"/>
@@ -1361,11 +1353,9 @@
     <row r="24" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A24" s="4"/>
       <c r="B24" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
-      <c r="G24" s="12">
-        <v>2</v>
-      </c>
+      <c r="G24" s="12"/>
       <c r="H24" s="12"/>
       <c r="I24" s="12"/>
       <c r="J24" s="12"/>
@@ -1377,11 +1367,9 @@
       <c r="P24" s="12"/>
       <c r="Q24" s="12"/>
       <c r="R24" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
-      <c r="X24" s="13" t="s">
-        <v>15</v>
-      </c>
+      <c r="X24" s="13"/>
       <c r="Y24" s="12"/>
       <c r="Z24" s="12"/>
       <c r="AA24" s="12"/>
@@ -1389,11 +1377,9 @@
       <c r="AC24" s="12"/>
       <c r="AD24" s="12"/>
       <c r="AE24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
-      <c r="AH24" s="14">
-        <v>2024</v>
-      </c>
+      <c r="AH24" s="14"/>
       <c r="AI24" s="14"/>
       <c r="AJ24" s="8"/>
       <c r="AK24" s="5"/>
